--- a/Team-Data/2014-15/2-10-2014-15.xlsx
+++ b/Team-Data/2014-15/2-10-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -766,13 +833,13 @@
         <v>4</v>
       </c>
       <c r="AM2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AN2" t="n">
         <v>1</v>
       </c>
       <c r="AO2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP2" t="n">
         <v>17</v>
@@ -784,7 +851,7 @@
         <v>30</v>
       </c>
       <c r="AS2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT2" t="n">
         <v>27</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-10-2014-15</t>
+          <t>2015-02-10</t>
         </is>
       </c>
     </row>
@@ -921,13 +988,13 @@
         <v>-1.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG3" t="n">
         <v>21</v>
@@ -975,7 +1042,7 @@
         <v>4</v>
       </c>
       <c r="AV3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW3" t="n">
         <v>10</v>
@@ -984,10 +1051,10 @@
         <v>28</v>
       </c>
       <c r="AY3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA3" t="n">
         <v>30</v>
@@ -996,7 +1063,7 @@
         <v>11</v>
       </c>
       <c r="BC3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-10-2014-15</t>
+          <t>2015-02-10</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E4" t="n">
         <v>21</v>
       </c>
       <c r="F4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G4" t="n">
-        <v>0.404</v>
+        <v>0.412</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
@@ -1052,22 +1119,22 @@
         <v>6.6</v>
       </c>
       <c r="M4" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="N4" t="n">
         <v>0.321</v>
       </c>
       <c r="O4" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="P4" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.742</v>
+        <v>0.741</v>
       </c>
       <c r="R4" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S4" t="n">
         <v>32</v>
@@ -1076,10 +1143,10 @@
         <v>41.8</v>
       </c>
       <c r="U4" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="V4" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="W4" t="n">
         <v>7</v>
@@ -1091,19 +1158,19 @@
         <v>4.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AA4" t="n">
         <v>19.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>95.5</v>
+        <v>95.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>-4</v>
+        <v>-3.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AE4" t="n">
         <v>19</v>
@@ -1136,10 +1203,10 @@
         <v>27</v>
       </c>
       <c r="AO4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AP4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ4" t="n">
         <v>22</v>
@@ -1154,31 +1221,31 @@
         <v>23</v>
       </c>
       <c r="AU4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AV4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AW4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX4" t="n">
         <v>23</v>
       </c>
       <c r="AY4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ4" t="n">
         <v>15</v>
       </c>
       <c r="BA4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-10-2014-15</t>
+          <t>2015-02-10</t>
         </is>
       </c>
     </row>
@@ -1207,55 +1274,55 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E5" t="n">
         <v>22</v>
       </c>
       <c r="F5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G5" t="n">
-        <v>0.423</v>
+        <v>0.431</v>
       </c>
       <c r="H5" t="n">
         <v>48.7</v>
       </c>
       <c r="I5" t="n">
-        <v>35.7</v>
+        <v>35.8</v>
       </c>
       <c r="J5" t="n">
-        <v>84.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.422</v>
+        <v>0.423</v>
       </c>
       <c r="L5" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="M5" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="N5" t="n">
-        <v>0.308</v>
+        <v>0.306</v>
       </c>
       <c r="O5" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="P5" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.736</v>
+        <v>0.735</v>
       </c>
       <c r="R5" t="n">
         <v>10.1</v>
       </c>
       <c r="S5" t="n">
-        <v>33.8</v>
+        <v>33.9</v>
       </c>
       <c r="T5" t="n">
-        <v>43.9</v>
+        <v>44</v>
       </c>
       <c r="U5" t="n">
         <v>20.3</v>
@@ -1264,10 +1331,10 @@
         <v>11.8</v>
       </c>
       <c r="W5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="X5" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y5" t="n">
         <v>5.4</v>
@@ -1279,25 +1346,25 @@
         <v>21.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>94.3</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.6</v>
+        <v>-2.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AE5" t="n">
         <v>17</v>
       </c>
       <c r="AF5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI5" t="n">
         <v>28</v>
@@ -1318,7 +1385,7 @@
         <v>30</v>
       </c>
       <c r="AO5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP5" t="n">
         <v>13</v>
@@ -1330,10 +1397,10 @@
         <v>23</v>
       </c>
       <c r="AS5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AU5" t="n">
         <v>25</v>
@@ -1348,7 +1415,7 @@
         <v>7</v>
       </c>
       <c r="AY5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ5" t="n">
         <v>4</v>
@@ -1360,7 +1427,7 @@
         <v>27</v>
       </c>
       <c r="BC5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-10-2014-15</t>
+          <t>2015-02-10</t>
         </is>
       </c>
     </row>
@@ -1389,28 +1456,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E6" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F6" t="n">
         <v>20</v>
       </c>
       <c r="G6" t="n">
-        <v>0.623</v>
+        <v>0.615</v>
       </c>
       <c r="H6" t="n">
         <v>48.7</v>
       </c>
       <c r="I6" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J6" t="n">
         <v>83.2</v>
       </c>
       <c r="K6" t="n">
-        <v>0.444</v>
+        <v>0.443</v>
       </c>
       <c r="L6" t="n">
         <v>7.7</v>
@@ -1422,34 +1489,34 @@
         <v>0.359</v>
       </c>
       <c r="O6" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="P6" t="n">
-        <v>26</v>
+        <v>26.2</v>
       </c>
       <c r="Q6" t="n">
         <v>0.784</v>
       </c>
       <c r="R6" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S6" t="n">
-        <v>33.6</v>
+        <v>33.7</v>
       </c>
       <c r="T6" t="n">
-        <v>45.5</v>
+        <v>45.8</v>
       </c>
       <c r="U6" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="V6" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="W6" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="X6" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="Y6" t="n">
         <v>5.5</v>
@@ -1458,25 +1525,25 @@
         <v>18.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AB6" t="n">
-        <v>102</v>
+        <v>101.9</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AE6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AF6" t="n">
         <v>10</v>
       </c>
       <c r="AG6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH6" t="n">
         <v>5</v>
@@ -1488,7 +1555,7 @@
         <v>18</v>
       </c>
       <c r="AK6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL6" t="n">
         <v>12</v>
@@ -1497,7 +1564,7 @@
         <v>16</v>
       </c>
       <c r="AN6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO6" t="n">
         <v>2</v>
@@ -1509,7 +1576,7 @@
         <v>3</v>
       </c>
       <c r="AR6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS6" t="n">
         <v>8</v>
@@ -1524,7 +1591,7 @@
         <v>13</v>
       </c>
       <c r="AW6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX6" t="n">
         <v>1</v>
@@ -1536,13 +1603,13 @@
         <v>1</v>
       </c>
       <c r="BA6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB6" t="n">
         <v>10</v>
       </c>
       <c r="BC6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-10-2014-15</t>
+          <t>2015-02-10</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1731,7 @@
         <v>27</v>
       </c>
       <c r="AI7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ7" t="n">
         <v>22</v>
@@ -1679,13 +1746,13 @@
         <v>7</v>
       </c>
       <c r="AN7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO7" t="n">
         <v>8</v>
       </c>
       <c r="AP7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ7" t="n">
         <v>16</v>
@@ -1706,13 +1773,13 @@
         <v>9</v>
       </c>
       <c r="AW7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX7" t="n">
         <v>25</v>
       </c>
       <c r="AY7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ7" t="n">
         <v>3</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-10-2014-15</t>
+          <t>2015-02-10</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E8" t="n">
         <v>35</v>
       </c>
       <c r="F8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G8" t="n">
-        <v>0.66</v>
+        <v>0.648</v>
       </c>
       <c r="H8" t="n">
         <v>48.6</v>
@@ -1771,7 +1838,7 @@
         <v>40.2</v>
       </c>
       <c r="J8" t="n">
-        <v>86.3</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="K8" t="n">
         <v>0.466</v>
@@ -1780,40 +1847,40 @@
         <v>9.699999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>27.1</v>
+        <v>27</v>
       </c>
       <c r="N8" t="n">
-        <v>0.357</v>
+        <v>0.358</v>
       </c>
       <c r="O8" t="n">
         <v>16.7</v>
       </c>
       <c r="P8" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.755</v>
+        <v>0.756</v>
       </c>
       <c r="R8" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S8" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T8" t="n">
-        <v>42.6</v>
+        <v>42.4</v>
       </c>
       <c r="U8" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="V8" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="W8" t="n">
         <v>8.1</v>
       </c>
       <c r="X8" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y8" t="n">
         <v>3.6</v>
@@ -1825,13 +1892,13 @@
         <v>21.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>106.8</v>
+        <v>106.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
         <v>4</v>
@@ -1843,13 +1910,13 @@
         <v>7</v>
       </c>
       <c r="AH8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AK8" t="n">
         <v>5</v>
@@ -1858,16 +1925,16 @@
         <v>6</v>
       </c>
       <c r="AM8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AO8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP8" t="n">
         <v>20</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>19</v>
       </c>
       <c r="AQ8" t="n">
         <v>15</v>
@@ -1876,10 +1943,10 @@
         <v>14</v>
       </c>
       <c r="AS8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT8" t="n">
         <v>20</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>19</v>
       </c>
       <c r="AU8" t="n">
         <v>8</v>
@@ -1894,13 +1961,13 @@
         <v>10</v>
       </c>
       <c r="AY8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ8" t="n">
         <v>14</v>
       </c>
       <c r="BA8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB8" t="n">
         <v>2</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-10-2014-15</t>
+          <t>2015-02-10</t>
         </is>
       </c>
     </row>
@@ -1935,61 +2002,61 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F9" t="n">
         <v>33</v>
       </c>
       <c r="G9" t="n">
-        <v>0.377</v>
+        <v>0.365</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
       </c>
       <c r="I9" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J9" t="n">
-        <v>86.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.434</v>
+        <v>0.432</v>
       </c>
       <c r="L9" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="M9" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="N9" t="n">
-        <v>0.316</v>
+        <v>0.317</v>
       </c>
       <c r="O9" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="P9" t="n">
         <v>24.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.74</v>
+        <v>0.741</v>
       </c>
       <c r="R9" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="S9" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
       <c r="T9" t="n">
-        <v>44.9</v>
+        <v>45.1</v>
       </c>
       <c r="U9" t="n">
         <v>21.6</v>
       </c>
       <c r="V9" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="W9" t="n">
         <v>7</v>
@@ -2004,40 +2071,40 @@
         <v>23.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>100.7</v>
+        <v>100.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>-3.4</v>
+        <v>-3.7</v>
       </c>
       <c r="AD9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>3</v>
       </c>
-      <c r="AE9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>6</v>
-      </c>
       <c r="AK9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AM9" t="n">
         <v>12</v>
@@ -2046,25 +2113,25 @@
         <v>28</v>
       </c>
       <c r="AO9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP9" t="n">
         <v>4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT9" t="n">
         <v>5</v>
       </c>
-      <c r="AS9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>6</v>
-      </c>
       <c r="AU9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AV9" t="n">
         <v>12</v>
@@ -2073,7 +2140,7 @@
         <v>23</v>
       </c>
       <c r="AX9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY9" t="n">
         <v>27</v>
@@ -2085,10 +2152,10 @@
         <v>10</v>
       </c>
       <c r="BB9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BC9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-10-2014-15</t>
+          <t>2015-02-10</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F10" t="n">
         <v>32</v>
       </c>
       <c r="G10" t="n">
-        <v>0.396</v>
+        <v>0.385</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
@@ -2135,34 +2202,34 @@
         <v>36.7</v>
       </c>
       <c r="J10" t="n">
-        <v>85.5</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="K10" t="n">
         <v>0.429</v>
       </c>
       <c r="L10" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="N10" t="n">
-        <v>0.343</v>
+        <v>0.344</v>
       </c>
       <c r="O10" t="n">
-        <v>16.5</v>
+        <v>16.3</v>
       </c>
       <c r="P10" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.712</v>
+        <v>0.707</v>
       </c>
       <c r="R10" t="n">
         <v>12.9</v>
       </c>
       <c r="S10" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="T10" t="n">
         <v>45.4</v>
@@ -2171,7 +2238,7 @@
         <v>21.4</v>
       </c>
       <c r="V10" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="W10" t="n">
         <v>7.8</v>
@@ -2180,7 +2247,7 @@
         <v>4.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z10" t="n">
         <v>18.9</v>
@@ -2189,16 +2256,16 @@
         <v>19.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>98.5</v>
+        <v>98.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.2</v>
+        <v>-1.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AE10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF10" t="n">
         <v>21</v>
@@ -2207,10 +2274,10 @@
         <v>20</v>
       </c>
       <c r="AH10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ10" t="n">
         <v>8</v>
@@ -2222,13 +2289,13 @@
         <v>10</v>
       </c>
       <c r="AM10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AN10" t="n">
         <v>19</v>
       </c>
       <c r="AO10" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AP10" t="n">
         <v>15</v>
@@ -2240,13 +2307,13 @@
         <v>1</v>
       </c>
       <c r="AS10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT10" t="n">
         <v>4</v>
       </c>
       <c r="AU10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV10" t="n">
         <v>8</v>
@@ -2270,7 +2337,7 @@
         <v>21</v>
       </c>
       <c r="BC10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-10-2014-15</t>
+          <t>2015-02-10</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>11.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -2404,19 +2471,19 @@
         <v>2</v>
       </c>
       <c r="AM11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN11" t="n">
         <v>2</v>
       </c>
       <c r="AO11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP11" t="n">
         <v>23</v>
       </c>
       <c r="AQ11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR11" t="n">
         <v>21</v>
@@ -2425,7 +2492,7 @@
         <v>2</v>
       </c>
       <c r="AT11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU11" t="n">
         <v>1</v>
@@ -2440,7 +2507,7 @@
         <v>2</v>
       </c>
       <c r="AY11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ11" t="n">
         <v>13</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-10-2014-15</t>
+          <t>2015-02-10</t>
         </is>
       </c>
     </row>
@@ -2496,49 +2563,49 @@
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>37</v>
+        <v>36.6</v>
       </c>
       <c r="J12" t="n">
-        <v>83.90000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="K12" t="n">
-        <v>0.441</v>
+        <v>0.439</v>
       </c>
       <c r="L12" t="n">
         <v>11.8</v>
       </c>
       <c r="M12" t="n">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
       <c r="N12" t="n">
         <v>0.353</v>
       </c>
       <c r="O12" t="n">
-        <v>17.4</v>
+        <v>17.7</v>
       </c>
       <c r="P12" t="n">
-        <v>24.2</v>
+        <v>24.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.718</v>
+        <v>0.717</v>
       </c>
       <c r="R12" t="n">
         <v>12</v>
       </c>
       <c r="S12" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="T12" t="n">
         <v>43.4</v>
       </c>
       <c r="U12" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="V12" t="n">
         <v>16.9</v>
       </c>
       <c r="W12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="X12" t="n">
         <v>4.5</v>
@@ -2547,19 +2614,19 @@
         <v>5.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.2</v>
+        <v>20.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>103.2</v>
+        <v>102.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE12" t="n">
         <v>4</v>
@@ -2574,10 +2641,10 @@
         <v>15</v>
       </c>
       <c r="AI12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AJ12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AK12" t="n">
         <v>22</v>
@@ -2589,19 +2656,19 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ12" t="n">
         <v>28</v>
       </c>
       <c r="AR12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AS12" t="n">
         <v>22</v>
@@ -2625,10 +2692,10 @@
         <v>26</v>
       </c>
       <c r="AZ12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BB12" t="n">
         <v>7</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-10-2014-15</t>
+          <t>2015-02-10</t>
         </is>
       </c>
     </row>
@@ -2744,25 +2811,25 @@
         <v>3</v>
       </c>
       <c r="AE13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG13" t="n">
         <v>22</v>
       </c>
       <c r="AH13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI13" t="n">
         <v>24</v>
       </c>
       <c r="AJ13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK13" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AL13" t="n">
         <v>22</v>
@@ -2795,7 +2862,7 @@
         <v>19</v>
       </c>
       <c r="AV13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW13" t="n">
         <v>29</v>
@@ -2804,7 +2871,7 @@
         <v>21</v>
       </c>
       <c r="AY13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ13" t="n">
         <v>16</v>
@@ -2813,10 +2880,10 @@
         <v>8</v>
       </c>
       <c r="BB13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-10-2014-15</t>
+          <t>2015-02-10</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2996,7 @@
         <v>8</v>
       </c>
       <c r="AF14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG14" t="n">
         <v>8</v>
@@ -2956,7 +3023,7 @@
         <v>5</v>
       </c>
       <c r="AO14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP14" t="n">
         <v>5</v>
@@ -2983,7 +3050,7 @@
         <v>12</v>
       </c>
       <c r="AX14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-10-2014-15</t>
+          <t>2015-02-10</t>
         </is>
       </c>
     </row>
@@ -3042,43 +3109,43 @@
         <v>48.7</v>
       </c>
       <c r="I15" t="n">
-        <v>37.4</v>
+        <v>37.2</v>
       </c>
       <c r="J15" t="n">
-        <v>86.2</v>
+        <v>86</v>
       </c>
       <c r="K15" t="n">
-        <v>0.434</v>
+        <v>0.433</v>
       </c>
       <c r="L15" t="n">
         <v>6.8</v>
       </c>
       <c r="M15" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="N15" t="n">
         <v>0.348</v>
       </c>
       <c r="O15" t="n">
-        <v>17.9</v>
+        <v>18.2</v>
       </c>
       <c r="P15" t="n">
-        <v>24.1</v>
+        <v>24.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.743</v>
+        <v>0.748</v>
       </c>
       <c r="R15" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="S15" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T15" t="n">
-        <v>43.7</v>
+        <v>43.5</v>
       </c>
       <c r="U15" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V15" t="n">
         <v>13.1</v>
@@ -3090,22 +3157,22 @@
         <v>4.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="AB15" t="n">
-        <v>99.5</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.7</v>
+        <v>-6.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3120,13 +3187,13 @@
         <v>3</v>
       </c>
       <c r="AI15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ15" t="n">
         <v>7</v>
       </c>
       <c r="AK15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL15" t="n">
         <v>23</v>
@@ -3141,40 +3208,40 @@
         <v>9</v>
       </c>
       <c r="AP15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR15" t="n">
         <v>8</v>
       </c>
       <c r="AS15" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AT15" t="n">
         <v>13</v>
       </c>
       <c r="AU15" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AV15" t="n">
         <v>7</v>
       </c>
       <c r="AW15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX15" t="n">
         <v>19</v>
       </c>
-      <c r="AX15" t="n">
-        <v>22</v>
-      </c>
       <c r="AY15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BB15" t="n">
         <v>19</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-10-2014-15</t>
+          <t>2015-02-10</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E16" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F16" t="n">
         <v>13</v>
       </c>
       <c r="G16" t="n">
-        <v>0.75</v>
+        <v>0.745</v>
       </c>
       <c r="H16" t="n">
         <v>48.9</v>
@@ -3230,16 +3297,16 @@
         <v>83.3</v>
       </c>
       <c r="K16" t="n">
-        <v>0.462</v>
+        <v>0.463</v>
       </c>
       <c r="L16" t="n">
         <v>5.4</v>
       </c>
       <c r="M16" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="N16" t="n">
-        <v>0.342</v>
+        <v>0.343</v>
       </c>
       <c r="O16" t="n">
         <v>18.5</v>
@@ -3248,28 +3315,28 @@
         <v>23.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.779</v>
+        <v>0.781</v>
       </c>
       <c r="R16" t="n">
         <v>10.6</v>
       </c>
       <c r="S16" t="n">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="T16" t="n">
-        <v>43.2</v>
+        <v>43.1</v>
       </c>
       <c r="U16" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="V16" t="n">
         <v>13</v>
       </c>
       <c r="W16" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="X16" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y16" t="n">
         <v>5.1</v>
@@ -3278,16 +3345,16 @@
         <v>19.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>100.8</v>
+        <v>100.9</v>
       </c>
       <c r="AC16" t="n">
         <v>5.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3299,13 +3366,13 @@
         <v>3</v>
       </c>
       <c r="AH16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK16" t="n">
         <v>7</v>
@@ -3314,7 +3381,7 @@
         <v>28</v>
       </c>
       <c r="AM16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AN16" t="n">
         <v>20</v>
@@ -3344,10 +3411,10 @@
         <v>5</v>
       </c>
       <c r="AW16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX16" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AY16" t="n">
         <v>20</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-10-2014-15</t>
+          <t>2015-02-10</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>-3.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE17" t="n">
         <v>17</v>
@@ -3490,10 +3557,10 @@
         <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM17" t="n">
         <v>21</v>
@@ -3502,13 +3569,13 @@
         <v>18</v>
       </c>
       <c r="AO17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP17" t="n">
         <v>14</v>
       </c>
       <c r="AQ17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR17" t="n">
         <v>29</v>
@@ -3538,13 +3605,13 @@
         <v>12</v>
       </c>
       <c r="BA17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB17" t="n">
         <v>28</v>
       </c>
       <c r="BC17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-10-2014-15</t>
+          <t>2015-02-10</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>1.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE18" t="n">
         <v>13</v>
@@ -3663,7 +3730,7 @@
         <v>13</v>
       </c>
       <c r="AH18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI18" t="n">
         <v>12</v>
@@ -3714,7 +3781,7 @@
         <v>12</v>
       </c>
       <c r="AY18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ18" t="n">
         <v>27</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-10-2014-15</t>
+          <t>2015-02-10</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="AD19" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE19" t="n">
         <v>29</v>
@@ -3845,10 +3912,10 @@
         <v>29</v>
       </c>
       <c r="AH19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI19" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AJ19" t="n">
         <v>11</v>
@@ -3875,7 +3942,7 @@
         <v>14</v>
       </c>
       <c r="AR19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AS19" t="n">
         <v>30</v>
@@ -3890,13 +3957,13 @@
         <v>26</v>
       </c>
       <c r="AW19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX19" t="n">
         <v>26</v>
       </c>
       <c r="AY19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ19" t="n">
         <v>11</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-10-2014-15</t>
+          <t>2015-02-10</t>
         </is>
       </c>
     </row>
@@ -3937,94 +4004,94 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F20" t="n">
         <v>25</v>
       </c>
       <c r="G20" t="n">
-        <v>0.51</v>
+        <v>0.519</v>
       </c>
       <c r="H20" t="n">
         <v>48.2</v>
       </c>
       <c r="I20" t="n">
-        <v>38</v>
+        <v>38.1</v>
       </c>
       <c r="J20" t="n">
-        <v>83.8</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.454</v>
+        <v>0.453</v>
       </c>
       <c r="L20" t="n">
         <v>6.8</v>
       </c>
       <c r="M20" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="N20" t="n">
-        <v>0.355</v>
+        <v>0.353</v>
       </c>
       <c r="O20" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P20" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.77</v>
+        <v>0.762</v>
       </c>
       <c r="R20" t="n">
-        <v>12.1</v>
+        <v>12.3</v>
       </c>
       <c r="S20" t="n">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="T20" t="n">
-        <v>43.9</v>
+        <v>44.3</v>
       </c>
       <c r="U20" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="V20" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="W20" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="X20" t="n">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="Y20" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Z20" t="n">
         <v>18.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AB20" t="n">
         <v>100</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="AE20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH20" t="n">
         <v>22</v>
@@ -4033,10 +4100,10 @@
         <v>11</v>
       </c>
       <c r="AJ20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK20" t="n">
         <v>14</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>13</v>
       </c>
       <c r="AL20" t="n">
         <v>24</v>
@@ -4045,7 +4112,7 @@
         <v>24</v>
       </c>
       <c r="AN20" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AO20" t="n">
         <v>15</v>
@@ -4054,28 +4121,28 @@
         <v>18</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AR20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV20" t="n">
         <v>6</v>
       </c>
       <c r="AW20" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AX20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY20" t="n">
         <v>30</v>
@@ -4087,7 +4154,7 @@
         <v>27</v>
       </c>
       <c r="BB20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC20" t="n">
         <v>16</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-10-2014-15</t>
+          <t>2015-02-10</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-7.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE21" t="n">
         <v>30</v>
@@ -4236,7 +4303,7 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR21" t="n">
         <v>16</v>
@@ -4248,10 +4315,10 @@
         <v>29</v>
       </c>
       <c r="AU21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW21" t="n">
         <v>21</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-10-2014-15</t>
+          <t>2015-02-10</t>
         </is>
       </c>
     </row>
@@ -4379,13 +4446,13 @@
         <v>1.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE22" t="n">
         <v>15</v>
       </c>
       <c r="AF22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG22" t="n">
         <v>15</v>
@@ -4400,7 +4467,7 @@
         <v>9</v>
       </c>
       <c r="AK22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL22" t="n">
         <v>16</v>
@@ -4409,7 +4476,7 @@
         <v>15</v>
       </c>
       <c r="AN22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO22" t="n">
         <v>10</v>
@@ -4439,19 +4506,19 @@
         <v>20</v>
       </c>
       <c r="AX22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY22" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AZ22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA22" t="n">
         <v>18</v>
       </c>
       <c r="BB22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC22" t="n">
         <v>14</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-10-2014-15</t>
+          <t>2015-02-10</t>
         </is>
       </c>
     </row>
@@ -4483,40 +4550,40 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E23" t="n">
         <v>16</v>
       </c>
       <c r="F23" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G23" t="n">
-        <v>0.296</v>
+        <v>0.291</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J23" t="n">
-        <v>81.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L23" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M23" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="N23" t="n">
         <v>0.358</v>
       </c>
       <c r="O23" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="P23" t="n">
         <v>19.3</v>
@@ -4525,16 +4592,16 @@
         <v>0.733</v>
       </c>
       <c r="R23" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="S23" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T23" t="n">
-        <v>40.5</v>
+        <v>40.7</v>
       </c>
       <c r="U23" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V23" t="n">
         <v>14.9</v>
@@ -4543,10 +4610,10 @@
         <v>7.6</v>
       </c>
       <c r="X23" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="Z23" t="n">
         <v>21.1</v>
@@ -4555,10 +4622,10 @@
         <v>18.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>96</v>
+        <v>95.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>-6</v>
+        <v>-6.2</v>
       </c>
       <c r="AD23" t="n">
         <v>1</v>
@@ -4567,7 +4634,7 @@
         <v>26</v>
       </c>
       <c r="AF23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG23" t="n">
         <v>26</v>
@@ -4576,16 +4643,16 @@
         <v>26</v>
       </c>
       <c r="AI23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ23" t="n">
         <v>23</v>
       </c>
       <c r="AK23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM23" t="n">
         <v>23</v>
@@ -4606,16 +4673,16 @@
         <v>28</v>
       </c>
       <c r="AS23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT23" t="n">
         <v>28</v>
       </c>
       <c r="AU23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV23" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AW23" t="n">
         <v>15</v>
@@ -4624,16 +4691,16 @@
         <v>30</v>
       </c>
       <c r="AY23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AZ23" t="n">
         <v>21</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>20</v>
       </c>
       <c r="BA23" t="n">
         <v>29</v>
       </c>
       <c r="BB23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC23" t="n">
         <v>26</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-10-2014-15</t>
+          <t>2015-02-10</t>
         </is>
       </c>
     </row>
@@ -4767,7 +4834,7 @@
         <v>30</v>
       </c>
       <c r="AL24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM24" t="n">
         <v>11</v>
@@ -4779,7 +4846,7 @@
         <v>21</v>
       </c>
       <c r="AP24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ24" t="n">
         <v>30</v>
@@ -4803,16 +4870,16 @@
         <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ24" t="n">
         <v>22</v>
       </c>
       <c r="BA24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-10-2014-15</t>
+          <t>2015-02-10</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E25" t="n">
         <v>29</v>
       </c>
       <c r="F25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G25" t="n">
-        <v>0.537</v>
+        <v>0.547</v>
       </c>
       <c r="H25" t="n">
         <v>48.6</v>
@@ -4868,37 +4935,37 @@
         <v>86.40000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>0.461</v>
+        <v>0.46</v>
       </c>
       <c r="L25" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="M25" t="n">
         <v>26.7</v>
       </c>
       <c r="N25" t="n">
-        <v>0.359</v>
+        <v>0.357</v>
       </c>
       <c r="O25" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="P25" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.785</v>
+        <v>0.784</v>
       </c>
       <c r="R25" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="S25" t="n">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="T25" t="n">
         <v>42.5</v>
       </c>
       <c r="U25" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="V25" t="n">
         <v>14.9</v>
@@ -4907,25 +4974,25 @@
         <v>8.800000000000001</v>
       </c>
       <c r="X25" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y25" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Z25" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AB25" t="n">
-        <v>105.9</v>
+        <v>105.7</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE25" t="n">
         <v>13</v>
@@ -4937,13 +5004,13 @@
         <v>14</v>
       </c>
       <c r="AH25" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AI25" t="n">
         <v>3</v>
       </c>
       <c r="AJ25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK25" t="n">
         <v>8</v>
@@ -4955,10 +5022,10 @@
         <v>5</v>
       </c>
       <c r="AN25" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AO25" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AP25" t="n">
         <v>25</v>
@@ -4970,16 +5037,16 @@
         <v>19</v>
       </c>
       <c r="AS25" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT25" t="n">
         <v>19</v>
       </c>
-      <c r="AT25" t="n">
-        <v>20</v>
-      </c>
       <c r="AU25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AV25" t="n">
         <v>22</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>23</v>
       </c>
       <c r="AW25" t="n">
         <v>6</v>
@@ -4994,10 +5061,10 @@
         <v>26</v>
       </c>
       <c r="BA25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC25" t="n">
         <v>15</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-10-2014-15</t>
+          <t>2015-02-10</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>5.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE26" t="n">
         <v>4</v>
@@ -5119,7 +5186,7 @@
         <v>5</v>
       </c>
       <c r="AH26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI26" t="n">
         <v>9</v>
@@ -5137,7 +5204,7 @@
         <v>2</v>
       </c>
       <c r="AN26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO26" t="n">
         <v>27</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-10-2014-15</t>
+          <t>2015-02-10</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E27" t="n">
         <v>18</v>
       </c>
       <c r="F27" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G27" t="n">
-        <v>0.353</v>
+        <v>0.36</v>
       </c>
       <c r="H27" t="n">
         <v>48.6</v>
@@ -5229,7 +5296,7 @@
         <v>36.1</v>
       </c>
       <c r="J27" t="n">
-        <v>80</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K27" t="n">
         <v>0.451</v>
@@ -5238,19 +5305,19 @@
         <v>5.1</v>
       </c>
       <c r="M27" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="N27" t="n">
-        <v>0.323</v>
+        <v>0.326</v>
       </c>
       <c r="O27" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="P27" t="n">
         <v>29.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.773</v>
+        <v>0.778</v>
       </c>
       <c r="R27" t="n">
         <v>10.8</v>
@@ -5268,34 +5335,34 @@
         <v>16.4</v>
       </c>
       <c r="W27" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="X27" t="n">
         <v>3.9</v>
       </c>
       <c r="Y27" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Z27" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>100</v>
+        <v>100.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>-4.1</v>
+        <v>-3.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
       </c>
       <c r="AF27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG27" t="n">
         <v>25</v>
@@ -5310,16 +5377,16 @@
         <v>28</v>
       </c>
       <c r="AK27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL27" t="n">
         <v>29</v>
       </c>
       <c r="AM27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AN27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO27" t="n">
         <v>1</v>
@@ -5328,13 +5395,13 @@
         <v>1</v>
       </c>
       <c r="AQ27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR27" t="n">
         <v>15</v>
       </c>
       <c r="AS27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT27" t="n">
         <v>8</v>
@@ -5346,7 +5413,7 @@
         <v>27</v>
       </c>
       <c r="AW27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX27" t="n">
         <v>29</v>
@@ -5355,7 +5422,7 @@
         <v>29</v>
       </c>
       <c r="AZ27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA27" t="n">
         <v>1</v>
@@ -5364,7 +5431,7 @@
         <v>16</v>
       </c>
       <c r="BC27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-10-2014-15</t>
+          <t>2015-02-10</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E28" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F28" t="n">
         <v>19</v>
       </c>
       <c r="G28" t="n">
-        <v>0.627</v>
+        <v>0.635</v>
       </c>
       <c r="H28" t="n">
         <v>48.9</v>
@@ -5411,49 +5478,49 @@
         <v>37.8</v>
       </c>
       <c r="J28" t="n">
-        <v>83.5</v>
+        <v>83.3</v>
       </c>
       <c r="K28" t="n">
-        <v>0.453</v>
+        <v>0.454</v>
       </c>
       <c r="L28" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="M28" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="N28" t="n">
-        <v>0.361</v>
+        <v>0.364</v>
       </c>
       <c r="O28" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="P28" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.765</v>
+        <v>0.766</v>
       </c>
       <c r="R28" t="n">
         <v>10.1</v>
       </c>
       <c r="S28" t="n">
-        <v>33.8</v>
+        <v>33.7</v>
       </c>
       <c r="T28" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
       <c r="U28" t="n">
         <v>24.3</v>
       </c>
       <c r="V28" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W28" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="X28" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y28" t="n">
         <v>4.8</v>
@@ -5471,28 +5538,28 @@
         <v>3.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="AE28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AF28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG28" t="n">
         <v>9</v>
       </c>
       <c r="AH28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI28" t="n">
         <v>13</v>
       </c>
       <c r="AJ28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL28" t="n">
         <v>11</v>
@@ -5501,25 +5568,25 @@
         <v>14</v>
       </c>
       <c r="AN28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP28" t="n">
         <v>22</v>
       </c>
       <c r="AQ28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR28" t="n">
         <v>25</v>
       </c>
       <c r="AS28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AT28" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AU28" t="n">
         <v>6</v>
@@ -5534,16 +5601,16 @@
         <v>8</v>
       </c>
       <c r="AY28" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ28" t="n">
         <v>9</v>
       </c>
       <c r="BA28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB28" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BC28" t="n">
         <v>8</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-10-2014-15</t>
+          <t>2015-02-10</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>4.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE29" t="n">
         <v>4</v>
@@ -5665,13 +5732,13 @@
         <v>5</v>
       </c>
       <c r="AH29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK29" t="n">
         <v>9</v>
@@ -5719,13 +5786,13 @@
         <v>19</v>
       </c>
       <c r="AZ29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA29" t="n">
         <v>5</v>
       </c>
       <c r="BB29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC29" t="n">
         <v>7</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-10-2014-15</t>
+          <t>2015-02-10</t>
         </is>
       </c>
     </row>
@@ -5835,16 +5902,16 @@
         <v>-2.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE30" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF30" t="n">
         <v>23</v>
       </c>
-      <c r="AF30" t="n">
-        <v>22</v>
-      </c>
       <c r="AG30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH30" t="n">
         <v>29</v>
@@ -5856,7 +5923,7 @@
         <v>29</v>
       </c>
       <c r="AK30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL30" t="n">
         <v>18</v>
@@ -5892,7 +5959,7 @@
         <v>25</v>
       </c>
       <c r="AW30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX30" t="n">
         <v>6</v>
@@ -5901,7 +5968,7 @@
         <v>18</v>
       </c>
       <c r="AZ30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA30" t="n">
         <v>25</v>
@@ -5910,7 +5977,7 @@
         <v>23</v>
       </c>
       <c r="BC30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-10-2014-15</t>
+          <t>2015-02-10</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6123,7 @@
         <v>21</v>
       </c>
       <c r="AQ31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR31" t="n">
         <v>22</v>
@@ -6065,13 +6132,13 @@
         <v>9</v>
       </c>
       <c r="AT31" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AU31" t="n">
         <v>5</v>
       </c>
       <c r="AV31" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AW31" t="n">
         <v>17</v>
@@ -6083,10 +6150,10 @@
         <v>7</v>
       </c>
       <c r="AZ31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB31" t="n">
         <v>18</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-10-2014-15</t>
+          <t>2015-02-10</t>
         </is>
       </c>
     </row>
